--- a/caterpillar-demand-quality/model/CAT_8Q_Operating_Dataset.xlsx
+++ b/caterpillar-demand-quality/model/CAT_8Q_Operating_Dataset.xlsx
@@ -320,7 +320,7 @@
     <t xml:space="preserve">Q1 2025: implied -1,078 (CI) against a company-wide swing of -1,300 (100 less 1,400). CI is 83% of the company-wide swing — consistent with Q1 2026, where the disclosed CI build is 75% of company-wide. FITS.</t>
   </si>
   <si>
-    <t xml:space="preserve">Q2 2026: implied +485 against a disclosed CI build of +400 with the prior-year quarter decreasing. The identity then implies a Q2 2025 CI build of about -85, which matches "dealer inventory decreased during the second quarter of 2025". FITS.</t>
+    <t xml:space="preserve">Q2 2026: implied +485 against a disclosed CI build of +400, with the prior-year quarter described only as a decrease (unquantified). The identity would imply a Q2 2025 CI build of about -85, directionally consistent with the disclosed "dealer inventory decreased during the second quarter of 2025" — but since that prior-year decrease was never quantified, this is a directional match, not a precise ~$85M reconciliation. FITS — $485M implied vs $400M disclosed build; prior-year decrease unquantified.</t>
   </si>
   <si>
     <t xml:space="preserve">Q3 2025: implied +233. No dollar disclosed, but the narrative is an increase in Q3 2025 against a decrease in Q3 2024. Sign agrees; magnitude untestable.</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">MOST LIKELY EXPLANATION, in order of size: (a) the $1.5B build is current-price while the gap is price-neutral — deflating by the 6.9% Q1 2026 price realization puts the swing near $1,400M and closes about a third of the difference; (b) reported CI sales include parts and services, so applying the retail percentage to the full reported base overstates retail dollars and understates the gap. Both are directionally measurable; neither is quantifiable from disclosure. UNRESOLVED residual after both: roughly $100-150M, about 2 points of growth.</t>
   </si>
   <si>
-    <t xml:space="preserve">Counter-evidence that the method is sound: Q2 2026 fits within $85M, and that residual implies a Q2 2025 CI build of about -85, which matches the disclosed "dealer inventory decreased during the second quarter of 2025." The method is not biased; Q1 2026 is the single quarter that does not close.</t>
+    <t xml:space="preserve">Counter-evidence that the method is sound: Q2 2026 is directionally consistent — the model implies a $485M swing versus a $400M disclosed current-quarter build, while the prior-year decrease was unquantified, consistent with the disclosed "dealer inventory decreased during the second quarter of 2025." The method is not biased; Q1 2026 is the single quarter that does not close.</t>
   </si>
   <si>
     <t xml:space="preserve">UNEXPLAINED RESIDUAL after the price-basis and parts/services adjustments: roughly $100-150M, about two points of growth. FX treatment on the retail side is unresolved and may account for part of it.</t>
@@ -2063,81 +2063,81 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
         <v>31</v>
       </c>

--- a/caterpillar-demand-quality/model/CAT_8Q_Operating_Dataset.xlsx
+++ b/caterpillar-demand-quality/model/CAT_8Q_Operating_Dataset.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="387">
   <si>
     <t xml:space="preserve">Caterpillar — Eight-Quarter Operating Dataset, Q3 2024 to Q2 2026</t>
   </si>
@@ -74,25 +74,25 @@
     <t xml:space="preserve">  DERIVED        calculated from sourced figures; the calculation is shown</t>
   </si>
   <si>
-    <t xml:space="preserve">  CALC           a live formula in this workbook; its inputs carry their own classification</t>
+    <t xml:space="preserve">  BACK-SOLVED    backed out as the residual of other disclosed figures because the filing gives it only rounded or not at all. Typed as a value in orange and flagged in a note. A bridge that uses one closes by construction and is NOT an independent check.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  NOT COLLECTED  left blank because it was not captured in this pass; it may exist in a filing. Never treated as zero.</t>
   </si>
   <si>
     <t xml:space="preserve">  NOT DISCLOSED  the company did not publish it. Left blank. Never estimated.</t>
   </si>
   <si>
-    <t xml:space="preserve">  INFERRED       used in notes, not as a cell value, where a scope or period qualifier could not be recovered from the filing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  ASSUMPTION is part of the project classification scheme but appears nowhere in this dataset. No figure here is assumed.</t>
+    <t xml:space="preserve">  CALC marks a live formula row (its inputs carry their own class). INFERRED is used in notes only, where a scope or period qualifier could not be recovered. No figure is an estimate; 4 figures are BACK-SOLVED (Consolidated I8, Construction Industries E6, Resource Industries E6, Power and Energy E7).</t>
   </si>
   <si>
     <t xml:space="preserve">RECONCILIATION</t>
   </si>
   <si>
-    <t xml:space="preserve">  Each segment tab carries a RECONCILIATION row: the disclosed volume, price realization, currency and inter-segment components,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  less the reported sales change. All 32 quarter-segment checks return zero. A non-zero value anywhere means the tab has been edited.</t>
+    <t xml:space="preserve">  Each bridge tab (three segments and the consolidated total) carries a RECONCILIATION row: disclosed volume, price realization, currency and inter-segment components, less the reported sales change. All 32 rows return zero; 28 reconcile independently.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  4 checks need caveats: 3 use a BACK-SOLVED prior-year value (CI, RI and P&amp;E Q2 2025) and close by construction; 1 depends on a component disclosed only as "$3.1B" (Consolidated Q2 2026). A non-zero value anywhere means the tab has been edited.</t>
   </si>
   <si>
     <t xml:space="preserve">THREE THINGS THAT WILL BREAK THIS DATASET IF IGNORED — see Comparability Log</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">Analysis — Construction Industries, formula-linked to the source tabs</t>
   </si>
   <si>
-    <t xml:space="preserve">Every cell below is a formula pointing at Consolidated / Construction Industries / Retail Statistics / Dealer Inventory / Cash Flow. No duplicated inputs.</t>
+    <t xml:space="preserve">Cells below are formulas pointing at Consolidated / Construction Industries / Retail Statistics / Dealer Inventory / Cash Flow, with three typed exceptions: row 20 (prior-year margins, from the releases), rows 41-42 (disclosed builds, from the Dealer Inventory tab quotes) and the 0.034 in I56 (the 340 bps disclosed on the Q2 2026 call).</t>
   </si>
   <si>
     <t xml:space="preserve">CI is used because it is the only segment unaffected by the restatement (see Comparability Log item 3).</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">CI price-adjusted sales growth %</t>
   </si>
   <si>
-    <t xml:space="preserve">ADJUSTED GAP: price-adj less retail (pts)</t>
+    <t xml:space="preserve">ADJUSTED GAP: price-adj less retail (pts; retail is disclosed in whole %, so about +/-0.5 pt)</t>
   </si>
   <si>
     <t xml:space="preserve">CI dealer inventory change $mm</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">OCF as % of consolidated sales</t>
   </si>
   <si>
-    <t xml:space="preserve">Management's stated primary volume driver</t>
+    <t xml:space="preserve">Volume driver mentioned first (order of mention only)</t>
   </si>
   <si>
     <t xml:space="preserve">Not captured</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">Q2 2026: "Higher sales volume was mainly driven by higher sales of equipment to end users and by the impact from changes in dealer inventories."</t>
   </si>
   <si>
-    <t xml:space="preserve">Caterpillar lists drivers in order of magnitude. The order inverts between these two quarters. That is the only direct evidence in the dataset.</t>
+    <t xml:space="preserve">INTERPRETIVE: the order of mention inverts between these two quarters (both quotes are SOURCED). Reading that order as relative magnitude is an analytical inference: Caterpillar does not say it lists drivers by size. Treat it as consistent with the dealer-inventory dollars, not as a measure of either driver.</t>
   </si>
   <si>
     <t xml:space="preserve">"Not captured" means the volume-driver sentence for that quarter has not been read from its release — NOT that no driver existed. Completing these six requires reading each release.</t>
@@ -290,10 +290,10 @@
     <t xml:space="preserve">VALIDATION TEST — does the gap actually measure dealer stocking?</t>
   </si>
   <si>
-    <t xml:space="preserve">Identity: sales to dealers = retail sales to end users + change in dealer inventory. Year over year, the DOLLAR gap below should therefore equal the change in the size of the build: build(t) less build(t-4). Row 40 is that gap in dollars. Rows 41-42 are what Caterpillar actually disclosed. Where both exist, the test is whether they agree.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implied stocking swing $mm (DERIVED from gap)</t>
+    <t xml:space="preserve">CONCEPTUAL RELATION, NOT AN ACCOUNTING IDENTITY: shipments to dealers are roughly retail sales to end users plus the change in dealer inventory. Because the two disclosures differ in price basis, scope, parts and services, and possibly currency (rows 33-36), row 40 is a DIRECTIONAL dollar estimate of the year-over-year change in the build, build(t) less build(t-4). Rows 41-42 are what Caterpillar actually disclosed. Only the SIGN can be tested against them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implied stocking swing $mm (DERIVED from gap; directional - retail rounding alone is about +/-$30M)</t>
   </si>
   <si>
     <t xml:space="preserve">Disclosed build, this quarter $mm (SOURCED)</t>
@@ -317,76 +317,76 @@
     <t xml:space="preserve">CI</t>
   </si>
   <si>
-    <t xml:space="preserve">Q1 2025: implied -1,078 (CI) against a company-wide swing of -1,300 (100 less 1,400). CI is 83% of the company-wide swing — consistent with Q1 2026, where the disclosed CI build is 75% of company-wide. FITS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q2 2026: implied +485 against a disclosed CI build of +400, with the prior-year quarter described only as a decrease (unquantified). The identity would imply a Q2 2025 CI build of about -85, directionally consistent with the disclosed "dealer inventory decreased during the second quarter of 2025" — but since that prior-year decrease was never quantified, this is a directional match, not a precise ~$85M reconciliation. FITS — $485M implied vs $400M disclosed build; prior-year decrease unquantified.</t>
+    <t xml:space="preserve">Q1 2025: implied -1,078 (CI estimate) against a company-wide swing of -1,300 (+100 less +1,400, both disclosed; the swing is DERIVED). SIGN AGREES. Scope differs (CI estimate vs company-wide disclosure), so magnitude is not tested.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q2 2026: implied +485 against a disclosed CI build of +400. The prior-year (Q2 2025) CI build has no dollar figure, only the CI North America narrative "dealer inventory decreased during the second quarter of 2025". SIGN AGREES; magnitude untestable.</t>
   </si>
   <si>
     <t xml:space="preserve">Q3 2025: implied +233. No dollar disclosed, but the narrative is an increase in Q3 2025 against a decrease in Q3 2024. Sign agrees; magnitude untestable.</t>
   </si>
   <si>
-    <t xml:space="preserve">Q1 2026: implied +1,258 against a disclosed CI build of +1,500 with the prior year a slight decrease, so the true swing is about +1,550. The gap UNDERSTATES by roughly 290.</t>
+    <t xml:space="preserve">Q1 2026: implied +1,258 against a disclosed CI build of +1,500; the prior-year quarter was a 'slight decrease' (unquantified), so the true swing exceeds +1,500 by an unknown amount. SIGN AGREES; magnitude untestable.</t>
   </si>
   <si>
     <t xml:space="preserve">REFUTED — this is NOT a retail recast. The only CI period appearing in BOTH filing vintages is Q2 2025, and it reads UP 2% in each. The same cross-vintage test DOES detect a change in the Power &amp; Energy Total (9% to 10%), so the test is sensitive enough to catch a recast — CI simply did not move. The 2026 realignment note concerns Rail / Resource Industries and Industrial, not Construction Industries.</t>
   </si>
   <si>
-    <t xml:space="preserve">MOST LIKELY EXPLANATION, in order of size: (a) the $1.5B build is current-price while the gap is price-neutral — deflating by the 6.9% Q1 2026 price realization puts the swing near $1,400M and closes about a third of the difference; (b) reported CI sales include parts and services, so applying the retail percentage to the full reported base overstates retail dollars and understates the gap. Both are directionally measurable; neither is quantifiable from disclosure. UNRESOLVED residual after both: roughly $100-150M, about 2 points of growth.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Counter-evidence that the method is sound: Q2 2026 is directionally consistent — the model implies a $485M swing versus a $400M disclosed current-quarter build, while the prior-year decrease was unquantified, consistent with the disclosed "dealer inventory decreased during the second quarter of 2025." The method is not biased; Q1 2026 is the single quarter that does not close.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNEXPLAINED RESIDUAL after the price-basis and parts/services adjustments: roughly $100-150M, about two points of growth. FX treatment on the retail side is unresolved and may account for part of it.</t>
+    <t xml:space="preserve">IF the Q1 2026 estimate falls short of the true swing (untestable, see row 48), likely contributors are: (a) the $1.5B build is current-price while the gap is price-neutral; (b) reported CI sales include parts and services, so applying the retail percentage to the full reported base overstates retail dollars and understates the gap. Both are directional; neither is quantifiable from disclosure. JUDGMENT, not a calculation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign agrees in all four testable quarters. No magnitude can be tested: each comparison either lacks a quantified prior-year CI build (Q1 2026, Q2 2026, Q3 2025) or mixes scopes (Q1 2025). The gap supports direction, not size.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNEXPLAINED RESIDUAL: not computable, because the prior-year builds are unquantified. FX treatment on the retail side is unresolved.</t>
   </si>
   <si>
     <t xml:space="preserve">CI MARGIN, REPORTED vs EX-TARIFF (Q4 2025 - Q2 2026 only)</t>
   </si>
   <si>
-    <t xml:space="preserve">Adds back the disclosed unfavorable manufacturing costs, which Caterpillar attributes largely to tariffs. DERIVED. Q2 2026 cannot be computed — no CI manufacturing-cost figure was disclosed.</t>
+    <t xml:space="preserve">Adds back the disclosed unfavorable manufacturing costs, which Caterpillar said largely reflected tariffs. DERIVED. Q2 2026 has no CI manufacturing-cost figure; column I instead uses the 340 bps tariff impact disclosed on the Q2 2026 call. DIFFERENT METHOD: column I is not comparable with G-H.</t>
   </si>
   <si>
     <t xml:space="preserve">Reported CI margin</t>
   </si>
   <si>
-    <t xml:space="preserve">Disclosed manufacturing-cost drag $mm</t>
+    <t xml:space="preserve">Tariff-related cost $mm: G-H disclosed mfg costs (largely tariffs, SOURCED); I = 340 bps x sales (DERIVED)</t>
   </si>
   <si>
     <t xml:space="preserve">CI margin excluding that drag</t>
   </si>
   <si>
-    <t xml:space="preserve">Distortion (bps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q4 2025 and Q1 2026 drags are SOURCED dollar figures from the releases. Q2 2026 is SOURCED as 340 bps from the Q2 2026 call (CFO Kyle Epley) and converted to dollars here — DERIVED.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">READ: Q4 2025 reported 14.9% is the series low, but ex-tariff it sits near 20.9% — inside the 19.6-20.4% band of the surrounding quarters. The trough is a cost shock, not demand or execution. It is NOT one-time: tariffs recur while in force. CI was still carrying 505 bps in Q1 2026 and 340 bps in Q2 2026, and management guides about 50% of Q3 2026 tariff costs into CI.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EX-TARIFF SEQUENCE: about 20.9% -&gt; 26.5% -&gt; 26.7%. Reported moves 14.9% -&gt; 21.4% -&gt; 23.3%, a gain of 840 bps. Roughly 270 bps of that is the tariff drag narrowing (606 to 340 bps); the remaining ~570 bps is volume leverage and price realization.</t>
+    <t xml:space="preserve">Tariff drag (bps): G-H workbook method; I = 340 bps disclosed on the call</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G-H are the disclosed unfavorable CI manufacturing-cost figures (SOURCED). Caterpillar said they 'largely reflected' higher tariff costs, so treating them as the full tariff effect is an approximation. I is the 340 bps disclosed on the Q2 2026 call (CFO Kyle Epley, SOURCED), converted to about $284M here (DERIVED). G-H and I use different methods; do not read them as a trend.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">READ (INTERPRETIVE): Q4 2025 reported 14.9% is the series low; ex-tariff it sits near 20.9%, inside the 19.6-20.4% band of the surrounding quarters. Our reading is that the trough was mainly a tariff cost shock rather than demand or execution; manufacturing costs are not purely tariffs, and the Q4 2025 profit bridge leaves a $14M unitemized residual. It is NOT one-time: tariffs recur while in force. CI was still carrying about 509 bps (workbook method) in Q1 2026 and 340 bps (disclosed) in Q2 2026. Q3 2026 CI tariff guidance: INSUFFICIENT EVIDENCE (no verbatim quote captured).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EX-TARIFF SEQUENCE: about 20.9% -&gt; 26.5% -&gt; 26.7%. Reported moves 14.9% -&gt; 21.4% -&gt; 23.3% (SOURCED), about 840 bps (DERIVED; +/-10 bps from one-decimal rounding). Lower tariff pressure and volume leverage with price realization both contributed (INTERPRETIVE), but the disclosures do not support a consistent split.</t>
   </si>
   <si>
     <t xml:space="preserve">CAVEAT — do not read ex-tariff margin as underlying performance. Price realization swung from -$60M to +$356M to +$309M largely to RECOVER tariffs. Removing the tariff cost while keeping the price taken to offset it double-counts the benefit. Ex-tariff margin is therefore an UPPER BOUND on underlying improvement. The cleanest genuine component is volume leverage.</t>
   </si>
   <si>
-    <t xml:space="preserve">IEEPA RECOVERIES — checked and cleared. Q2 2026 operating profit included $392M of expected IEEPA tariff recoveries, but CFO Kyle Epley stated "the majority of this amount reflected in corporate items." Segment margins, including the CI 23.3%, are therefore NOT materially inflated by it. The recovery IS one-time; the tariff costs are not. Full-year 2026 tariff cost guided to about $2.2 billion.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEADLINE: Q4 2025 CI reported margin 14.9%, tariff drag ~604 bps. Q1 2026 ~509 bps. Q2 2026 ~343 bps. Ex-tariff: ~20.9% / ~26.5% / ~26.7%.</t>
+    <t xml:space="preserve">IEEPA RECOVERIES: Q2 2026 operating profit included $392M of expected IEEPA tariff recoveries (SOURCED). CFO Kyle Epley stated "the majority of this amount reflected in corporate items" (SOURCED). The CI share was not disclosed, so CI segment margin (23.3%) is unlikely to be materially affected; that is an INFERENCE, not a confirmed exclusion. The recovery IS one-time; the tariff costs are not. FY2026 tariff cost guidance (about $2.2B): INSUFFICIENT EVIDENCE (no verbatim quote captured).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEADLINE: Q4 2025 CI reported margin 14.9%, tariff-related drag ~604 bps (workbook method). Q1 2026 ~509 bps (workbook method). Q2 2026 340 bps (disclosed on the call). Ex-tariff: ~20.9% / ~26.5% / ~26.7% (upper bound, see row 62).</t>
   </si>
   <si>
     <t xml:space="preserve">VERDICT ON THE MARGIN QUESTION</t>
   </si>
   <si>
-    <t xml:space="preserve">BOTH, and the split is roughly one-third / two-thirds. Normalization from a tariff-depressed base accounts for about 270 bps of the 840 bps recovery. The rest is volume leverage plus price realization — real, but partly price taken to recover an external cost, so it should be described as "price recovering tariffs plus volume leverage", never as efficiency or cost control.</t>
+    <t xml:space="preserve">BOTH contributed, and the split cannot be measured on a consistent basis. Normalization from a tariff-depressed base is part of the recovery; volume leverage plus price realization is the rest, real but partly price taken to recover an external cost, so it should be described as "price recovering tariffs plus volume leverage", never as efficiency or cost control.</t>
   </si>
   <si>
     <t xml:space="preserve">Consolidated Sales &amp; Revenues ($mm)</t>
   </si>
   <si>
-    <t xml:space="preserve">Blue = sourced. Black = formula. The reconciliation row is the integrity check: components must equal the change.</t>
+    <t xml:space="preserve">Blue = sourced. Orange = BACK-SOLVED (see note below). Black = formula. The reconciliation row is the integrity check: components must equal the change. A column with a back-solved component closes by construction.</t>
   </si>
   <si>
     <t xml:space="preserve">Line</t>
@@ -404,6 +404,9 @@
     <t xml:space="preserve">Sales volume</t>
   </si>
   <si>
+    <t xml:space="preserve">SOURCED (I8: BACK-SOLVED)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Price realization</t>
   </si>
   <si>
@@ -419,7 +422,7 @@
     <t xml:space="preserve">RECONCILIATION (must be 0)</t>
   </si>
   <si>
-    <t xml:space="preserve">Q2 2026 sales volume of 3,113 is DERIVED: the release rounds it to "$3.1 billion", so it is backed out as the residual of the disclosed total.</t>
+    <t xml:space="preserve">Q2 2026 sales volume of 3,113 is BACK-SOLVED: the release rounds it to "$3.1 billion", so it is backed out as the residual of the disclosed total. The Q2 2026 reconciliation therefore holds only within the rounding of that disclosure; it is not an independent check. Shown in orange.</t>
   </si>
   <si>
     <t xml:space="preserve">Operating cash flow and capex are disclosed year-to-date, not per quarter — see the Cash Flow tab for what exists.</t>
@@ -437,6 +440,9 @@
     <t xml:space="preserve">Prior-year segment sales</t>
   </si>
   <si>
+    <t xml:space="preserve">SOURCED (E6: BACK-SOLVED)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Volume</t>
   </si>
   <si>
@@ -449,7 +455,7 @@
     <t xml:space="preserve">Segment profit margin</t>
   </si>
   <si>
-    <t xml:space="preserve">Q2 2024 prior-year sales of 6,683 is DERIVED: 6,190 less the sum of the four disclosed Q2 2025 change components.</t>
+    <t xml:space="preserve">Q2 2024 prior-year sales of 6,683 is BACK-SOLVED: 6,190 less the sum of the four disclosed Q2 2025 change components. The Q2 2025 reconciliation therefore closes by construction; it is not an independent check. Shown in orange.</t>
   </si>
   <si>
     <t xml:space="preserve">SEGMENT PROFIT BRIDGE — as disclosed by Caterpillar (SOURCED)</t>
@@ -497,7 +503,7 @@
     <t xml:space="preserve">Shaded columns are post-restatement and are not comparable with the unshaded ones. Q2 2025 prior-year was not captured; left blank rather than estimated.</t>
   </si>
   <si>
-    <t xml:space="preserve">Q2 2024 prior-year of 3,206 is DERIVED: Q2 2025 sales less the four disclosed change components. Shown in orange.</t>
+    <t xml:space="preserve">Q2 2024 prior-year of 3,206 is BACK-SOLVED: Q2 2025 sales less the four disclosed change components. The Q2 2025 reconciliation therefore closes by construction; it is not an independent check. Shown in orange.</t>
   </si>
   <si>
     <t xml:space="preserve">Energy &amp; Transportation / Power &amp; Energy ($mm) — RENAMED AND RESTATED</t>
@@ -515,10 +521,13 @@
     <t xml:space="preserve">P&amp;E</t>
   </si>
   <si>
+    <t xml:space="preserve">SOURCED (E7: BACK-SOLVED)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Shaded = post-restatement. Q2 2025 prior-year not captured; left blank.</t>
   </si>
   <si>
-    <t xml:space="preserve">Q2 2024 prior-year of 7,337 is DERIVED: Q2 2025 sales less the four disclosed change components. Shown in orange.</t>
+    <t xml:space="preserve">Q2 2024 prior-year of 7,337 is BACK-SOLVED: Q2 2025 sales less the four disclosed change components. The Q2 2025 reconciliation therefore closes by construction; it is not an independent check. Shown in orange.</t>
   </si>
   <si>
     <t xml:space="preserve">Dealer Inventory Change — disclosure is inconsistent across quarters</t>
@@ -884,7 +893,7 @@
     <t xml:space="preserve">throughout</t>
   </si>
   <si>
-    <t xml:space="preserve">Company-wide dollar figures appear in Q4 2024, Q1 2025 and Q4 2025 only. Q2 2026 has a CI-only figure from the earnings call.</t>
+    <t xml:space="preserve">Company-wide dollar figures appear in Q4 2024, Q1 2025, Q4 2025 and Q1 2026. CI dollar figures appear in Q1 2026 and Q2 2026 only (both in the 10-Qs, corroborated on the calls).</t>
   </si>
   <si>
     <t xml:space="preserve">No continuous dollar series is possible.</t>
@@ -908,7 +917,7 @@
     <t xml:space="preserve">Dealer inventory scope changes mid-series</t>
   </si>
   <si>
-    <t xml:space="preserve">Q4 2024 / Q1 2025 / Q4 2025 disclose a COMPANY-WIDE dollar change. Q1 2026 and Q2 2026 disclose a CONSTRUCTION INDUSTRIES figure only.</t>
+    <t xml:space="preserve">Q4 2024 / Q1 2025 / Q4 2025 disclose a COMPANY-WIDE dollar change. Q1 2026 discloses both scopes. Q2 2026 discloses a CONSTRUCTION INDUSTRIES figure only.</t>
   </si>
   <si>
     <t xml:space="preserve">The two are different scopes; charting them as one line would be wrong.</t>
@@ -998,16 +1007,16 @@
     <t xml:space="preserve">15</t>
   </si>
   <si>
-    <t xml:space="preserve">Q4 2025 CI margin depressed by tariff costs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4Q25 release, CI: "unfavorable manufacturing costs of $420 million ... largely reflected the impact of higher tariffs." 1Q26 release, CI: $362 million, same attribution. 2Q26 call, CFO Kyle Epley: CI margin "impacted by ... 340 basis points within Construction Industries."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reported CI margin of 14.9% in Q4 2025 is a cost shock, not demand weakness or operating deterioration. Ex-tariff it sits near 20.9%, inside the 19.6-20.4% band of the surrounding quarters. Using the reported series as a baseline overstates the 2026 recovery.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ex-tariff margin shown on the Analysis tab for all three quarters. NOT a one-time item — tariffs recur while in force, guided to about $2.2bn for FY2026 with roughly half of Q3 landing in CI.</t>
+    <t xml:space="preserve">Q4 2025 CI margin depressed by manufacturing costs largely attributed to tariffs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4Q25 release, CI: "unfavorable manufacturing costs of $420 million ... largely reflected the impact of higher tariffs." 1Q26 release, CI: $362 million, same attribution. 2Q26 call, CFO Kyle Epley: CI margin "impacted by ... 340 basis points within Construction Industries." Exact release wording INSUFFICIENT EVIDENCE: the CI tab (A28) quotes "...higher tariff costs."; re-check against the releases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Our reading (INTERPRETIVE): reported CI margin of 14.9% in Q4 2025 was mainly a tariff cost shock rather than demand weakness or operating deterioration; the disclosed manufacturing costs only 'largely' reflected tariffs. Ex-tariff it sits near 20.9%, inside the 19.6-20.4% band of the surrounding quarters. Using the reported series as a baseline overstates the 2026 recovery.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ex-tariff margin shown on the Analysis tab for all three quarters (Q2 2026 on a different method). NOT a one-time item: tariffs recur while in force. FY2026 tariff guidance (about $2.2bn, roughly half of Q3 in CI) was recorded without a verbatim quote: INSUFFICIENT EVIDENCE, not used in the analysis.</t>
   </si>
   <si>
     <t xml:space="preserve">16</t>
@@ -1019,10 +1028,10 @@
     <t xml:space="preserve">Q2 2026 release: "Operating profit in the second quarter of 2026 included $392 million of expected International Emergency Economic Power Act (IEEPA) tariff recoveries." Call, CFO Kyle Epley: "with the majority of this amount reflected in corporate items."</t>
   </si>
   <si>
-    <t xml:space="preserve">A one-time credit of this size would inflate Q2 2026 margins if it sat in the segments. It does not — it is mostly in corporate items, so CI margin is unaffected.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consolidated operating margin for Q2 2026 must be described as including a one-time recovery. CI segment margin needs no adjustment. CI tariff COST of 340 bps is separate and still a drag.</t>
+    <t xml:space="preserve">A one-time credit of this size would inflate Q2 2026 margins if it sat in the segments. The CFO said the majority is in corporate items; the CI share was not disclosed, so CI margin is unlikely to be materially affected (INFERENCE).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consolidated operating margin for Q2 2026 must be described as including a one-time recovery. The CI share of the $392M was not disclosed; with the majority in corporate items, CI segment margin is unlikely to be materially affected (INFERENCE; no adjustment made). CI tariff COST of 340 bps is separate and still a drag.</t>
   </si>
   <si>
     <t xml:space="preserve">Source Index — every document used</t>
@@ -1136,7 +1145,7 @@
     <t xml:space="preserve">https://www.fool.com/earnings/call-transcripts/2026/08/11/caterpillar-cat-q2-2026-earnings-call-transcript/</t>
   </si>
   <si>
-    <t xml:space="preserve">CI dealer inventory +$400M, Q4 drawdown commentary</t>
+    <t xml:space="preserve">CI dealer inventory +$400M. Q4 drawdown commentary: no verbatim quote captured, INSUFFICIENT EVIDENCE; not used as a finding.</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.fool.com/earnings/call-transcripts/2026/04/30/caterpillar-cat-q1-2026-earnings-transcript/</t>
@@ -1169,10 +1178,10 @@
     <t xml:space="preserve">PRE-2026 retail basis wording; recast test</t>
   </si>
   <si>
-    <t xml:space="preserve">CI profit bridge: volume +322, price -60, mfg costs -420 (tariffs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI profit bridge: volume +505, price +356, mfg costs -362 (tariffs)</t>
+    <t xml:space="preserve">CI profit bridge: volume +322, price -60, mfg costs -420 (largely attributed to tariffs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI profit bridge: volume +505, price +356, mfg costs -362 (largely attributed to tariffs)</t>
   </si>
   <si>
     <t xml:space="preserve">CI profit: volume only; no mfg-cost driver disclosed</t>
@@ -1181,7 +1190,7 @@
     <t xml:space="preserve">Q2 2026 Earnings Call Transcript</t>
   </si>
   <si>
-    <t xml:space="preserve">CI tariff impact 340 bps; IEEPA $392M mostly in corporate items; FY26 tariff cost ~$2.2B</t>
+    <t xml:space="preserve">CI tariff impact 340 bps; IEEPA $392M, majority in corporate items. FY26 tariff cost ~$2.2B: no verbatim quote captured, INSUFFICIENT EVIDENCE.</t>
   </si>
 </sst>
 </file>
@@ -2173,27 +2182,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2201,19 +2210,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C4" s="56" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2221,19 +2230,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C5" s="56" t="s">
         <v>42</v>
       </c>
       <c r="D5" s="56" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E5" s="56" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F5" s="56" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2241,19 +2250,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C6" s="56" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D6" s="56" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E6" s="56" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F6" s="56" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2261,19 +2270,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C7" s="56" t="s">
         <v>40</v>
       </c>
       <c r="D7" s="56" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E7" s="56" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F7" s="56" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2281,19 +2290,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C8" s="56" t="s">
         <v>42</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E8" s="56" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F8" s="56" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2301,19 +2310,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="56" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C9" s="56" t="s">
         <v>40</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E9" s="56" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F9" s="56" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2321,19 +2330,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C10" s="56" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E10" s="56" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F10" s="56" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2341,19 +2350,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="56" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C11" s="56" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D11" s="56" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E11" s="56" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F11" s="56" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2361,19 +2370,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C12" s="56" t="s">
         <v>42</v>
       </c>
       <c r="D12" s="56" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E12" s="56" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F12" s="56" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2381,19 +2390,19 @@
         <v>10</v>
       </c>
       <c r="B13" s="57" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C13" s="56" t="s">
         <v>43</v>
       </c>
       <c r="D13" s="56" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E13" s="56" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F13" s="56" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2401,119 +2410,119 @@
         <v>11</v>
       </c>
       <c r="B14" s="57" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C14" s="56" t="s">
         <v>39</v>
       </c>
       <c r="D14" s="56" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E14" s="56" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F14" s="56" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="56" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B15" s="57" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C15" s="56" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D15" s="56" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E15" s="56" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="F15" s="56" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="56" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B16" s="57" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C16" s="56" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D16" s="56" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E16" s="56" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F16" s="56" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="73.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="56" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B17" s="57" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C17" s="56" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D17" s="56" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E17" s="56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F17" s="56" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="56" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B18" s="57" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C18" s="56" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D18" s="56" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E18" s="56" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F18" s="56" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="56" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B19" s="57" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C19" s="56" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D19" s="56" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E19" s="56" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F19" s="56" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -2545,21 +2554,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2567,13 +2576,13 @@
         <v>36</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C4" s="59" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D4" s="60" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2581,13 +2590,13 @@
         <v>37</v>
       </c>
       <c r="B5" s="56" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D5" s="60" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2595,13 +2604,13 @@
         <v>38</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D6" s="60" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2609,13 +2618,13 @@
         <v>39</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C7" s="59" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D7" s="60" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2623,13 +2632,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="D8" s="60" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2637,13 +2646,13 @@
         <v>41</v>
       </c>
       <c r="B9" s="56" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C9" s="59" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D9" s="60" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2651,13 +2660,13 @@
         <v>42</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D10" s="60" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2665,13 +2674,13 @@
         <v>43</v>
       </c>
       <c r="B11" s="56" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C11" s="59" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D11" s="60" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2679,13 +2688,13 @@
         <v>39</v>
       </c>
       <c r="B12" s="56" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D12" s="60" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2693,13 +2702,13 @@
         <v>43</v>
       </c>
       <c r="B13" s="56" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C13" s="59" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D13" s="60" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2707,13 +2716,13 @@
         <v>43</v>
       </c>
       <c r="B14" s="56" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D14" s="60" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2721,13 +2730,13 @@
         <v>43</v>
       </c>
       <c r="B15" s="56" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C15" s="61" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D15" s="56" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2735,13 +2744,13 @@
         <v>43</v>
       </c>
       <c r="B16" s="56" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D16" s="60" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2749,13 +2758,13 @@
         <v>42</v>
       </c>
       <c r="B17" s="56" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C17" s="59" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D17" s="60" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2763,27 +2772,27 @@
         <v>42</v>
       </c>
       <c r="B18" s="56" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C18" s="61" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D18" s="56" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="62" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B19" s="62" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C19" s="62" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D19" s="62" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2791,13 +2800,13 @@
         <v>39</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2805,13 +2814,13 @@
         <v>41</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2819,13 +2828,13 @@
         <v>42</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2833,13 +2842,13 @@
         <v>43</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2847,13 +2856,13 @@
         <v>43</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -3830,8 +3839,8 @@
         <v>509.071358748778</v>
       </c>
       <c r="I58" s="36" t="n">
-        <f aca="false">(I57-I55)*10000</f>
-        <v>342.854061826024</v>
+        <f aca="false">I56/'Construction Industries'!I5*10000</f>
+        <v>340</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4070,16 +4079,16 @@
       <c r="H8" s="26" t="n">
         <v>2318</v>
       </c>
-      <c r="I8" s="26" t="n">
+      <c r="I8" s="27" t="n">
         <v>3113</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B9" s="26" t="n">
         <v>104</v>
@@ -4111,7 +4120,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B10" s="26" t="n">
         <v>-102</v>
@@ -4143,7 +4152,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B11" s="26" t="n">
         <v>53</v>
@@ -4175,7 +4184,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B12" s="21" t="n">
         <f aca="false">SUM(B8:B11)</f>
@@ -4215,7 +4224,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B13" s="21" t="n">
         <f aca="false">B7-B12</f>
@@ -4255,12 +4264,12 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="37" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -4290,12 +4299,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="38" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4332,7 +4341,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B5" s="26" t="n">
         <v>6345</v>
@@ -4364,7 +4373,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B6" s="26" t="n">
         <v>6999</v>
@@ -4375,7 +4384,7 @@
       <c r="D6" s="26" t="n">
         <v>6424</v>
       </c>
-      <c r="E6" s="26" t="n">
+      <c r="E6" s="27" t="n">
         <v>6683</v>
       </c>
       <c r="F6" s="26" t="n">
@@ -4391,7 +4400,7 @@
         <v>6190</v>
       </c>
       <c r="J6" s="18" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4436,7 +4445,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B8" s="26" t="n">
         <v>-458</v>
@@ -4468,7 +4477,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B9" s="26" t="n">
         <v>-147</v>
@@ -4500,7 +4509,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B10" s="26" t="n">
         <v>-64</v>
@@ -4532,7 +4541,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B11" s="26" t="n">
         <v>15</v>
@@ -4564,7 +4573,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B12" s="21" t="n">
         <f aca="false">SUM(B8:B11)</f>
@@ -4604,7 +4613,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B13" s="21" t="n">
         <f aca="false">B7-B12</f>
@@ -4644,7 +4653,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B14" s="26" t="n">
         <v>1486</v>
@@ -4676,7 +4685,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B15" s="23" t="n">
         <v>0.234</v>
@@ -4708,22 +4717,22 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="37" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G21" s="21" t="n">
         <v>322</v>
@@ -4735,7 +4744,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G22" s="21" t="n">
         <v>-60</v>
@@ -4747,7 +4756,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G23" s="21" t="n">
         <v>-420</v>
@@ -4756,12 +4765,12 @@
         <v>-362</v>
       </c>
       <c r="I23" s="40" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G24" s="39" t="n">
         <f aca="false">SUM(G21:G23)</f>
@@ -4775,7 +4784,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G25" s="39" t="n">
         <f aca="false">G14-C14</f>
@@ -4792,7 +4801,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G26" s="39" t="n">
         <f aca="false">G25-G24</f>
@@ -4809,12 +4818,12 @@
     </row>
     <row r="28" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="29" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="41" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -4844,12 +4853,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="22" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4886,7 +4895,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B5" s="26" t="n">
         <v>3028</v>
@@ -4918,7 +4927,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B6" s="26" t="n">
         <v>3351</v>
@@ -4945,7 +4954,7 @@
         <v>3886</v>
       </c>
       <c r="J6" s="18" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4990,7 +4999,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B8" s="26" t="n">
         <v>-352</v>
@@ -5022,7 +5031,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B9" s="26" t="n">
         <v>38</v>
@@ -5054,7 +5063,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B10" s="26" t="n">
         <v>-11</v>
@@ -5086,7 +5095,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B11" s="26" t="n">
         <v>2</v>
@@ -5118,7 +5127,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B12" s="21" t="n">
         <f aca="false">SUM(B8:B11)</f>
@@ -5158,7 +5167,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B13" s="21" t="n">
         <f aca="false">B7-B12</f>
@@ -5198,7 +5207,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B14" s="26" t="n">
         <v>619</v>
@@ -5230,7 +5239,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B15" s="23" t="n">
         <v>0.204</v>
@@ -5262,12 +5271,12 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="22" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="37" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -5297,12 +5306,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="22" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5339,31 +5348,31 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B5" s="45" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C5" s="45" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D5" s="45" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E5" s="45" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F5" s="45" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G5" s="45" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H5" s="46" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I5" s="46" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J5" s="18" t="s">
         <v>66</v>
@@ -5371,7 +5380,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B6" s="26" t="n">
         <v>7187</v>
@@ -5403,7 +5412,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B7" s="26" t="n">
         <v>6859</v>
@@ -5430,7 +5439,7 @@
         <v>7037</v>
       </c>
       <c r="J7" s="18" t="s">
-        <v>66</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5475,7 +5484,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B9" s="26" t="n">
         <v>57</v>
@@ -5507,7 +5516,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B10" s="26" t="n">
         <v>213</v>
@@ -5539,7 +5548,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B11" s="26" t="n">
         <v>-20</v>
@@ -5571,7 +5580,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B12" s="26" t="n">
         <v>78</v>
@@ -5603,7 +5612,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B13" s="21" t="n">
         <f aca="false">SUM(B9:B12)</f>
@@ -5643,7 +5652,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14" s="21" t="n">
         <f aca="false">B8-B13</f>
@@ -5683,7 +5692,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B15" s="26" t="n">
         <v>1433</v>
@@ -5715,7 +5724,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B16" s="23" t="n">
         <v>0.199</v>
@@ -5747,12 +5756,12 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="22" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="37" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -5788,38 +5797,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F3" s="14" t="s">
         <v>44</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5828,20 +5837,20 @@
       </c>
       <c r="B4" s="47"/>
       <c r="C4" s="15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D4" s="48" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G4" s="24"/>
       <c r="H4" s="49" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5855,17 +5864,17 @@
         <v>93</v>
       </c>
       <c r="D5" s="48" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>66</v>
       </c>
       <c r="G5" s="24"/>
       <c r="H5" s="49" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5879,17 +5888,17 @@
         <v>93</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F6" s="18" t="s">
         <v>66</v>
       </c>
       <c r="G6" s="24"/>
       <c r="H6" s="49" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5898,20 +5907,20 @@
       </c>
       <c r="B7" s="47"/>
       <c r="C7" s="15" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D7" s="48" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G7" s="24"/>
       <c r="H7" s="49" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5920,20 +5929,20 @@
       </c>
       <c r="B8" s="47"/>
       <c r="C8" s="15" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D8" s="48" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G8" s="24"/>
       <c r="H8" s="49" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5947,17 +5956,17 @@
         <v>93</v>
       </c>
       <c r="D9" s="48" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F9" s="18" t="s">
         <v>66</v>
       </c>
       <c r="G9" s="24"/>
       <c r="H9" s="49" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5968,13 +5977,13 @@
         <v>2000</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D10" s="48" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F10" s="18" t="s">
         <v>66</v>
@@ -5983,7 +5992,7 @@
         <v>1500</v>
       </c>
       <c r="H10" s="41" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5992,37 +6001,37 @@
       </c>
       <c r="B11" s="47"/>
       <c r="C11" s="15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D11" s="48" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G11" s="21" t="n">
         <v>400</v>
       </c>
       <c r="H11" s="41" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="22" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="32" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="22" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -6052,32 +6061,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="50" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="50" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>36</v>
@@ -6109,7 +6118,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B7" s="23" t="n">
         <v>-0.08</v>
@@ -6141,7 +6150,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B8" s="23" t="n">
         <v>0.06</v>
@@ -6173,7 +6182,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B9" s="23" t="n">
         <v>-0.12</v>
@@ -6205,7 +6214,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B10" s="23" t="n">
         <v>-0.07</v>
@@ -6237,7 +6246,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B11" s="23" t="n">
         <v>-0.07</v>
@@ -6269,7 +6278,7 @@
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>36</v>
@@ -6301,7 +6310,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B14" s="23" t="n">
         <v>0.11</v>
@@ -6333,7 +6342,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B15" s="23" t="n">
         <v>0.1</v>
@@ -6365,7 +6374,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B16" s="23" t="n">
         <v>-0.29</v>
@@ -6397,7 +6406,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B17" s="23" t="n">
         <v>0.25</v>
@@ -6421,7 +6430,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B18" s="23" t="n">
         <v>0.05</v>
@@ -6453,12 +6462,12 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="22" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="41" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -6491,29 +6500,29 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F4" s="14" t="s">
         <v>44</v>
@@ -6521,7 +6530,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B5" s="26" t="n">
         <v>8642</v>
@@ -6533,7 +6542,7 @@
         <v>893</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>66</v>
@@ -6541,7 +6550,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B6" s="26" t="n">
         <v>3600</v>
@@ -6549,7 +6558,7 @@
       <c r="C6" s="47"/>
       <c r="D6" s="47"/>
       <c r="E6" s="12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F6" s="18" t="s">
         <v>66</v>
@@ -6557,7 +6566,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B7" s="26" t="n">
         <v>1289</v>
@@ -6569,7 +6578,7 @@
         <v>208</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F7" s="18" t="s">
         <v>66</v>
@@ -6577,7 +6586,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B8" s="26" t="n">
         <v>4411</v>
@@ -6587,7 +6596,7 @@
       </c>
       <c r="D8" s="47"/>
       <c r="E8" s="12" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F8" s="18" t="s">
         <v>66</v>
@@ -6595,7 +6604,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B9" s="26" t="n">
         <v>8148</v>
@@ -6607,7 +6616,7 @@
         <v>1021</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F9" s="18" t="s">
         <v>66</v>
@@ -6615,7 +6624,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B10" s="26" t="n">
         <v>11739</v>
@@ -6625,7 +6634,7 @@
       </c>
       <c r="D10" s="47"/>
       <c r="E10" s="12" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F10" s="18" t="s">
         <v>66</v>
@@ -6633,7 +6642,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B11" s="26" t="n">
         <v>1870</v>
@@ -6643,7 +6652,7 @@
       </c>
       <c r="D11" s="47"/>
       <c r="E11" s="12" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="F11" s="18" t="s">
         <v>66</v>
@@ -6651,7 +6660,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B12" s="26" t="n">
         <v>6241</v>
@@ -6661,7 +6670,7 @@
       </c>
       <c r="D12" s="47"/>
       <c r="E12" s="12" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F12" s="18" t="s">
         <v>66</v>
@@ -6669,7 +6678,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="52" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B13" s="52" t="n">
         <f aca="false">B5-B6</f>
@@ -6678,39 +6687,39 @@
       <c r="C13" s="52"/>
       <c r="D13" s="52"/>
       <c r="E13" s="52" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F13" s="53" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="22" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E19" s="14" t="s">
         <v>44</v>
@@ -6718,7 +6727,7 @@
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="54" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B20" s="27"/>
       <c r="D20" s="49"/>
@@ -6737,10 +6746,10 @@
         <v>1163</v>
       </c>
       <c r="D21" s="49" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6753,10 +6762,10 @@
       </c>
       <c r="C22" s="24"/>
       <c r="D22" s="49" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6772,10 +6781,10 @@
         <v>898</v>
       </c>
       <c r="D23" s="49" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6791,20 +6800,20 @@
         <v>587</v>
       </c>
       <c r="D24" s="49" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E24" s="28" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="22" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="22" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/caterpillar-demand-quality/model/CAT_8Q_Operating_Dataset.xlsx
+++ b/caterpillar-demand-quality/model/CAT_8Q_Operating_Dataset.xlsx
@@ -362,7 +362,7 @@
     <t xml:space="preserve">G-H are the disclosed unfavorable CI manufacturing-cost figures (SOURCED). Caterpillar said they 'largely reflected' higher tariff costs, so treating them as the full tariff effect is an approximation. I is the 340 bps disclosed on the Q2 2026 call (CFO Kyle Epley, SOURCED), converted to about $284M here (DERIVED). G-H and I use different methods; do not read them as a trend.</t>
   </si>
   <si>
-    <t xml:space="preserve">READ (INTERPRETIVE): Q4 2025 reported 14.9% is the series low; ex-tariff it sits near 20.9%, inside the 19.6-20.4% band of the surrounding quarters. Our reading is that the trough was mainly a tariff cost shock rather than demand or execution; manufacturing costs are not purely tariffs, and the Q4 2025 profit bridge leaves a $14M unitemized residual. It is NOT one-time: tariffs recur while in force. CI was still carrying about 509 bps (workbook method) in Q1 2026 and 340 bps (disclosed) in Q2 2026. Q3 2026 CI tariff guidance: INSUFFICIENT EVIDENCE (no verbatim quote captured).</t>
+    <t xml:space="preserve">READ (INTERPRETIVE): Q4 2025 reported 14.9% is the series low; ex-tariff it sits near 20.9%, inside the 19.6-20.4% band of the surrounding quarters. Our reading is that the trough was mainly a tariff cost shock rather than demand or execution; manufacturing costs are not purely tariffs, and the Q4 2025 profit bridge leaves a $14M unitemized residual. It is NOT one-time: tariffs recur while in force. CI was still carrying about 509 bps (workbook method) in Q1 2026 and 340 bps (disclosed) in Q2 2026. For Q3 2026, management expects tariff costs of around $600 million with about 50% incurred in Construction Industries (CFO Kyle Epley, Q2 2026 call).</t>
   </si>
   <si>
     <t xml:space="preserve">EX-TARIFF SEQUENCE: about 20.9% -&gt; 26.5% -&gt; 26.7%. Reported moves 14.9% -&gt; 21.4% -&gt; 23.3% (SOURCED), about 840 bps (DERIVED; +/-10 bps from one-decimal rounding). Lower tariff pressure and volume leverage with price realization both contributed (INTERPRETIVE), but the disclosures do not support a consistent split.</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">CAVEAT — do not read ex-tariff margin as underlying performance. Price realization swung from -$60M to +$356M to +$309M largely to RECOVER tariffs. Removing the tariff cost while keeping the price taken to offset it double-counts the benefit. Ex-tariff margin is therefore an UPPER BOUND on underlying improvement. The cleanest genuine component is volume leverage.</t>
   </si>
   <si>
-    <t xml:space="preserve">IEEPA RECOVERIES: Q2 2026 operating profit included $392M of expected IEEPA tariff recoveries (SOURCED). CFO Kyle Epley stated "the majority of this amount reflected in corporate items" (SOURCED). The CI share was not disclosed, so CI segment margin (23.3%) is unlikely to be materially affected; that is an INFERENCE, not a confirmed exclusion. The recovery IS one-time; the tariff costs are not. FY2026 tariff cost guidance (about $2.2B): INSUFFICIENT EVIDENCE (no verbatim quote captured).</t>
+    <t xml:space="preserve">IEEPA RECOVERIES: Q2 2026 operating profit included $392M of expected IEEPA tariff recoveries (SOURCED). CFO Kyle Epley stated "the majority of this amount reflected in corporate items" (SOURCED). The CI share was not disclosed, so CI segment margin (23.3%) is unlikely to be materially affected; that is an INFERENCE, not a confirmed exclusion. The recovery IS one-time; the tariff costs are not. Management expects full-year 2026 tariff costs of around $2.2 billion, excluding approximately $400 million of expected IEEPA tariff recoveries, at the low end of its prior range (CFO Kyle Epley, Q2 2026 call).</t>
   </si>
   <si>
     <t xml:space="preserve">HEADLINE: Q4 2025 CI reported margin 14.9%, tariff-related drag ~604 bps (workbook method). Q1 2026 ~509 bps (workbook method). Q2 2026 340 bps (disclosed on the call). Ex-tariff: ~20.9% / ~26.5% / ~26.7% (upper bound, see row 62).</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">CI only</t>
   </si>
   <si>
-    <t xml:space="preserve">10-Q: "Construction Industries dealer inventory increased by $400 million"  |  Call (corroborating): "Dealer inventory increased by about $400 million in Construction Industries."</t>
+    <t xml:space="preserve">10-Q: "Construction Industries dealer inventory increased by $400 million"  |  Call (corroborating): "Dealer inventory increased by $400 million in Construction Industries compared to a decrease in the second quarter of 2025."</t>
   </si>
   <si>
     <t xml:space="preserve">Q2 2026 Form 10-Q, Item 2 MD&amp;A — accession 0000018230-26-000046; corroborated by Q2 2026 earnings call</t>
@@ -1016,7 +1016,7 @@
     <t xml:space="preserve">Our reading (INTERPRETIVE): reported CI margin of 14.9% in Q4 2025 was mainly a tariff cost shock rather than demand weakness or operating deterioration; the disclosed manufacturing costs only 'largely' reflected tariffs. Ex-tariff it sits near 20.9%, inside the 19.6-20.4% band of the surrounding quarters. Using the reported series as a baseline overstates the 2026 recovery.</t>
   </si>
   <si>
-    <t xml:space="preserve">Ex-tariff margin shown on the Analysis tab for all three quarters (Q2 2026 on a different method). NOT a one-time item: tariffs recur while in force. FY2026 tariff guidance (about $2.2bn, roughly half of Q3 in CI) was recorded without a verbatim quote: INSUFFICIENT EVIDENCE, not used in the analysis.</t>
+    <t xml:space="preserve">Ex-tariff margin shown on the Analysis tab for all three quarters (Q2 2026 on a different method). NOT a one-time item: tariffs recur while in force. Management expects full-year 2026 tariff costs of around $2.2 billion, excluding approximately $400 million of expected IEEPA tariff recoveries, at the low end of its prior range; for Q3 2026 it expects tariff costs of around $600 million with about 50% incurred in Construction Industries (CFO Kyle Epley, Q2 2026 call).</t>
   </si>
   <si>
     <t xml:space="preserve">16</t>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">https://www.fool.com/earnings/call-transcripts/2026/08/11/caterpillar-cat-q2-2026-earnings-call-transcript/</t>
   </si>
   <si>
-    <t xml:space="preserve">CI dealer inventory +$400M. Q4 drawdown commentary: no verbatim quote captured, INSUFFICIENT EVIDENCE; not used as a finding.</t>
+    <t xml:space="preserve">CI dealer inventory +$400M. Q4 2026 CI dealer-inventory drawdown expected: CFO Kyle Epley, "a more typical reduction in Construction Industries dealer inventory of over $1 billion in the fourth quarter"; CEO Joseph Creed, "We'll have a drawdown in the fourth quarter on CI dealer inventory."</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.fool.com/earnings/call-transcripts/2026/04/30/caterpillar-cat-q1-2026-earnings-transcript/</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">Q2 2026 Earnings Call Transcript</t>
   </si>
   <si>
-    <t xml:space="preserve">CI tariff impact 340 bps; IEEPA $392M, majority in corporate items. FY26 tariff cost ~$2.2B: no verbatim quote captured, INSUFFICIENT EVIDENCE.</t>
+    <t xml:space="preserve">CI tariff impact 340 bps; IEEPA $392M, majority in corporate items. FY2026 tariff costs expected around $2.2B, excluding approximately $400M of expected IEEPA tariff recoveries, at the low end of the prior range; Q3 2026 tariff costs expected around $600M, about 50% in CI (CFO Kyle Epley).</t>
   </si>
 </sst>
 </file>
